--- a/outputs/ranking.xlsx
+++ b/outputs/ranking.xlsx
@@ -819,25 +819,25 @@
         <v>100</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>230.94</v>
+        <v>234.87</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>368.5276403432546</v>
+        <v>369.961485385814</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>731.9435783334552</v>
+        <v>726.1672811888071</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>550.2356093383548</v>
+        <v>548.0643832873105</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.595772236698946</v>
+        <v>0.5751755668489547</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>2.169410142606111</v>
+        <v>2.091783885506055</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>1.382591189652528</v>
+        <v>1.333479726177505</v>
       </c>
       <c r="N5" s="5" t="n">
         <v>100</v>
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="Q5" s="10" t="n">
-        <v>3.133654760726173</v>
+        <v>3.196240666874038</v>
       </c>
       <c r="R5" s="10" t="n">
-        <v>11.11226324121541</v>
+        <v>11.02027321156658</v>
       </c>
     </row>
     <row r="6">
@@ -885,25 +885,25 @@
         <v>86.11111111111111</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>245.2</v>
+        <v>250.23</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>375.290185086368</v>
+        <v>376.475391259613</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>317.3556904500454</v>
+        <v>321.4303455698741</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>346.3229377682067</v>
+        <v>348.9528684147435</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.5305472474974227</v>
+        <v>0.5045174090221516</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.2942727995515717</v>
+        <v>0.2845396058421219</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>0.412410023524497</v>
+        <v>0.3945285074321365</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>94.44444444444444</v>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="Q6" s="10" t="n">
-        <v>3.998773008877109</v>
+        <v>4.081135540241491</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>5.180269640728783</v>
+        <v>5.246989087938717</v>
       </c>
     </row>
     <row r="7">
@@ -948,34 +948,34 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>86.11111111111111</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>190.81</v>
+        <v>197.82</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>224.9967635437312</v>
+        <v>225.4372808167587</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>278.4375931255703</v>
+        <v>279.3540013212914</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>251.7171783346508</v>
+        <v>252.3956410690251</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.179166519279551</v>
+        <v>0.1396081327305565</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.4592400457291039</v>
+        <v>0.4121625787144447</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>0.3192032825043276</v>
+        <v>0.2758853557225005</v>
       </c>
       <c r="N7" s="5" t="n">
         <v>83.33333333333334</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>88.88888888888889</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="Q7" s="10" t="n">
-        <v>4.601477513839215</v>
+        <v>4.780065394245846</v>
       </c>
       <c r="R7" s="10" t="n">
-        <v>6.83389000654657</v>
+        <v>6.857236780948141</v>
       </c>
     </row>
     <row r="8">
@@ -1017,25 +1017,25 @@
         <v>77.77777777777777</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>166.32</v>
+        <v>170.91</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>240.1854844351954</v>
+        <v>244.9519902855507</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>202.2355035901655</v>
+        <v>207.2082811020749</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>221.2104940126805</v>
+        <v>226.0801356938128</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.4441166692832816</v>
+        <v>0.433222106872335</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.2159421812780515</v>
+        <v>0.2123824299460235</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>0.3300294252806666</v>
+        <v>0.3228022684091791</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>88.88888888888889</v>
@@ -1049,16 +1049,16 @@
         </is>
       </c>
       <c r="Q8" s="10" t="n">
-        <v>5.129153217228216</v>
+        <v>5.184206022372479</v>
       </c>
       <c r="R8" s="10" t="n">
-        <v>6.261213856852391</v>
+        <v>6.309297181976995</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlassian Corporation</t>
+          <t>ServiceNow, Inc.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1080,34 +1080,34 @@
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>72.22222222222223</v>
+        <v>75</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>207.82</v>
+        <v>105.12</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>141.4740191013711</v>
+        <v>104.3503592141274</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>337.4541120988237</v>
+        <v>156.8415810449708</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>239.4640656000974</v>
+        <v>130.5959701295491</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>-0.3192473337437632</v>
+        <v>-0.0073215447666723</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.623780733802443</v>
+        <v>0.4920241728022339</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>0.1522667000293398</v>
+        <v>0.2423513140177809</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>50</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>94.44444444444444</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1115,16 +1115,16 @@
         </is>
       </c>
       <c r="Q9" s="10" t="n">
-        <v>8.883454913853628</v>
+        <v>7.856065682181051</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>14.45123702322237</v>
+        <v>11.89904736141527</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DocuSign, Inc.</t>
+          <t>Atlassian Corporation</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Maturing</t>
+          <t>Growth, profitable</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1146,51 +1146,51 @@
         </is>
       </c>
       <c r="F10" s="7" t="n">
-        <v>69.44444444444446</v>
+        <v>69.44444444444444</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>74.65000000000001</v>
+        <v>191.72</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>86.87108647176464</v>
+        <v>142.2428072390134</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>81.69323636035655</v>
+        <v>335.0416354310466</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>84.2821614160606</v>
-      </c>
-      <c r="K10" s="9" t="n">
-        <v>0.163711808061147</v>
+        <v>238.6422213350301</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>-0.2580700644741631</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.09435011869198329</v>
+        <v>0.7475570385512551</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>0.1290309633765652</v>
+        <v>0.2447434870385461</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>77.77777777777779</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>61.11111111111111</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q10" s="10" t="n">
-        <v>4.172772737446687</v>
+        <v>8.191960082839509</v>
       </c>
       <c r="R10" s="10" t="n">
-        <v>4.584241042180023</v>
+        <v>14.34762084931938</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Zscaler, Inc.</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>High growth, unprofitable</t>
+          <t>Mature, profitable</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -1215,48 +1215,48 @@
         <v>63.88888888888889</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>207.38</v>
+        <v>229.17</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>139.7575856628418</v>
+        <v>253.667259410066</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>276.6081035466023</v>
+        <v>251.3618087033946</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>208.182844604722</v>
-      </c>
-      <c r="K11" s="11" t="n">
-        <v>-0.3260797296612896</v>
+        <v>252.5145340567303</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0.106895577126439</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.3338224686401887</v>
+        <v>0.0968355749155414</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.003871369489449661</v>
+        <v>0.1018655760209903</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>44.44444444444444</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>83.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q11" s="10" t="n">
-        <v>11.6982158822047</v>
+        <v>4.693575265158591</v>
       </c>
       <c r="R11" s="10" t="n">
-        <v>15.51661838958482</v>
+        <v>5.136630834597295</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>DOCU</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>DocuSign, Inc.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mature, profitable</t>
+          <t>Maturing</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -1281,48 +1281,48 @@
         <v>58.33333333333333</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>240.7</v>
+        <v>82.17</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>252.0023071272865</v>
+        <v>87.16774073265853</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>245.9451550812153</v>
+        <v>82.00014098364184</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>248.9737311042509</v>
+        <v>84.58394085815019</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.0469559913888097</v>
-      </c>
-      <c r="L12" s="9" t="n">
-        <v>0.02179125501128087</v>
+        <v>0.0608219634009801</v>
+      </c>
+      <c r="L12" s="11" t="n">
+        <v>-0.002067165831302953</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>0.03437362320004556</v>
+        <v>0.02937739878483847</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>66.66666666666666</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>50</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q12" s="10" t="n">
-        <v>4.923769620571291</v>
+        <v>4.612093448924637</v>
       </c>
       <c r="R12" s="10" t="n">
-        <v>5.028488220445414</v>
+        <v>4.602170227026895</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ServiceNow, Inc.</t>
+          <t>Twilio Inc.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Growth, profitable</t>
+          <t>Maturing</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -1347,31 +1347,31 @@
         <v>55.55555555555556</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>141.97</v>
+        <v>205.03</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>104.1082226487905</v>
+        <v>155.9086794421973</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>155.2478866843261</v>
+        <v>238.1692925726628</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>129.6780546665583</v>
+        <v>197.03898600743</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>-0.2666885775248959</v>
+        <v>-0.2395811371887173</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.09352600327059291</v>
+        <v>0.1616314323399639</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>-0.08658128712715152</v>
+        <v>-0.03897485242437682</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>55.55555555555556</v>
+        <v>50</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>55.55555555555556</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>10.69320613827384</v>
+        <v>5.922275313090807</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>11.72705933607786</v>
+        <v>6.926647350545215</v>
       </c>
     </row>
     <row r="14">
@@ -1410,34 +1410,34 @@
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>50</v>
+        <v>49.99999999999999</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>94.19</v>
+        <v>95.5</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>99.29075218174428</v>
+        <v>99.65141074225843</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>80.56623659789955</v>
+        <v>82.0007558710136</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>89.92849438982191</v>
+        <v>90.82608330663601</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.0541538611502736</v>
+        <v>0.0434702695524444</v>
       </c>
       <c r="L14" s="11" t="n">
-        <v>-0.1446412931532057</v>
+        <v>-0.1413533416647791</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>-0.04524371600146604</v>
+        <v>-0.04894153605616747</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>72.22222222222221</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>27.77777777777778</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1445,16 +1445,16 @@
         </is>
       </c>
       <c r="Q14" s="10" t="n">
-        <v>4.053362204581053</v>
+        <v>4.13214383345701</v>
       </c>
       <c r="R14" s="10" t="n">
-        <v>3.234043076989192</v>
+        <v>3.320313226982331</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>PAYC</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Paycom Software, Inc.</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mature, profitable</t>
+          <t>High growth, unprofitable</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -1476,51 +1476,51 @@
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>47.22222222222222</v>
+        <v>47.22222222222221</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>251.64</v>
+        <v>352.96</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>244.8288102149409</v>
+        <v>162.276496012086</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>224.152740967558</v>
+        <v>428.5607491976577</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>234.4907755912494</v>
+        <v>295.4186226048719</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>-0.027067198319262</v>
-      </c>
-      <c r="L15" s="11" t="n">
-        <v>-0.109232471119226</v>
+        <v>-0.540241115106284</v>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>0.2141906992227385</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>-0.06814983471924407</v>
+        <v>-0.1630252079417728</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>61.11111111111111</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>33.33333333333333</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q15" s="10" t="n">
-        <v>5.347673613101331</v>
+        <v>10.73755837380588</v>
       </c>
       <c r="R15" s="10" t="n">
-        <v>4.743835216254207</v>
+        <v>13.24823963326811</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>Zscaler, Inc.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1542,34 +1542,34 @@
         </is>
       </c>
       <c r="F16" s="7" t="n">
-        <v>47.22222222222221</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>337.57</v>
+        <v>237.83</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>161.5431765829726</v>
+        <v>139.4439977617566</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>436.6919251098618</v>
+        <v>266.0360438983563</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>299.1175508464172</v>
+        <v>202.7400208300564</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>-0.5214528050982832</v>
+        <v>-0.4136820512056655</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.2936336911155073</v>
+        <v>0.1185975019903136</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>-0.1139095569913878</v>
+        <v>-0.147542274607676</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>22.22222222222222</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>72.22222222222221</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1577,16 +1577,16 @@
         </is>
       </c>
       <c r="Q16" s="10" t="n">
-        <v>10.22646096341891</v>
+        <v>13.37774189559688</v>
       </c>
       <c r="R16" s="10" t="n">
-        <v>13.51827451568381</v>
+        <v>14.93349784577565</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>PAYC</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Twilio Inc.</t>
+          <t>Paycom Software, Inc.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Maturing</t>
+          <t>Mature, profitable</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -1608,34 +1608,34 @@
         </is>
       </c>
       <c r="F17" s="7" t="n">
-        <v>38.88888888888889</v>
+        <v>41.66666666666667</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>244.37</v>
+        <v>264.2</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>154.6167574404823</v>
+        <v>245.6528149111778</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>234.0939313535321</v>
+        <v>226.3620019932689</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>194.3553443970072</v>
+        <v>236.0074084522234</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>-0.3672842106621832</v>
+        <v>-0.0702013061651104</v>
       </c>
       <c r="L17" s="11" t="n">
-        <v>-0.04205126916752422</v>
+        <v>-0.1432172521072334</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>-0.2046677399148538</v>
+        <v>-0.1067092791361719</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>33.33333333333333</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>44.44444444444444</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q17" s="10" t="n">
-        <v>7.114575450838921</v>
+        <v>5.623591628405713</v>
       </c>
       <c r="R17" s="10" t="n">
-        <v>6.803132608771344</v>
+        <v>4.79236873892657</v>
       </c>
     </row>
     <row r="18">
@@ -1677,25 +1677,25 @@
         <v>27.77777777777778</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>310.36</v>
+        <v>312.96</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>197.5974096073511</v>
+        <v>198.2899815049556</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>197.7891274834339</v>
+        <v>197.6061996583332</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>197.6932685453925</v>
+        <v>197.9480905816444</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>-0.3633283618786213</v>
+        <v>-0.3664047114488892</v>
       </c>
       <c r="L18" s="11" t="n">
-        <v>-0.3627106344779162</v>
+        <v>-0.3685895972062461</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>-0.3630194981782687</v>
+        <v>-0.3674971543275677</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>38.88888888888889</v>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q18" s="10" t="n">
-        <v>13.83480677407914</v>
+        <v>13.96811173430613</v>
       </c>
       <c r="R18" s="10" t="n">
-        <v>8.063216873573712</v>
+        <v>8.053838715896836</v>
       </c>
     </row>
     <row r="19">
@@ -1743,25 +1743,25 @@
         <v>25</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>306.84</v>
+        <v>306.08</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>88.86755023366669</v>
+        <v>89.23124019187139</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>278.7801540506846</v>
+        <v>269.3621347108286</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>183.8238521421757</v>
+        <v>179.29668745135</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>-0.7103782093805674</v>
+        <v>-0.7084708566653444</v>
       </c>
       <c r="L19" s="11" t="n">
-        <v>-0.09144780976833311</v>
+        <v>-0.1199616612949929</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>-0.4009130095744503</v>
+        <v>-0.4142162589801686</v>
       </c>
       <c r="N19" s="5" t="n">
         <v>11.11111111111111</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q19" s="10" t="n">
-        <v>23.17396364875435</v>
+        <v>23.11562095109607</v>
       </c>
       <c r="R19" s="10" t="n">
-        <v>21.0199366412188</v>
+        <v>20.29695721196258</v>
       </c>
     </row>
     <row r="20">
@@ -1809,25 +1809,25 @@
         <v>19.44444444444444</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>187.26</v>
+        <v>208.24</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>103.61134294969</v>
+        <v>103.8633934378699</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>98.47521083209057</v>
+        <v>98.47813979322858</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>101.0432768908903</v>
+        <v>101.1707666155492</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>-0.4466979443036956</v>
+        <v>-0.5012322635522961</v>
       </c>
       <c r="L20" s="11" t="n">
-        <v>-0.4741257565305427</v>
+        <v>-0.5270930666863783</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>-0.4604118504171191</v>
+        <v>-0.5141626651193372</v>
       </c>
       <c r="N20" s="5" t="n">
         <v>27.77777777777778</v>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q20" s="10" t="n">
-        <v>11.13936460934935</v>
+        <v>12.40705484282382</v>
       </c>
       <c r="R20" s="10" t="n">
-        <v>5.774657417682138</v>
+        <v>5.774834679924379</v>
       </c>
     </row>
     <row r="21">
@@ -1875,25 +1875,25 @@
         <v>19.44444444444444</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>247.11</v>
+        <v>235.27</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>72.51888335827871</v>
+        <v>72.86128834260121</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>182.6327886974033</v>
+        <v>179.5441165386042</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>127.575836027841</v>
+        <v>126.2027024406027</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>-0.7065319762118947</v>
+        <v>-0.6903077810915068</v>
       </c>
       <c r="L21" s="11" t="n">
-        <v>-0.2609251398267844</v>
+        <v>-0.236859282787418</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>-0.4837285580193396</v>
+        <v>-0.4635835319394623</v>
       </c>
       <c r="N21" s="5" t="n">
         <v>16.66666666666666</v>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q21" s="10" t="n">
-        <v>24.87181460790544</v>
+        <v>23.63129893865413</v>
       </c>
       <c r="R21" s="10" t="n">
-        <v>18.11631771760847</v>
+        <v>17.79270811442963</v>
       </c>
     </row>
     <row r="22">
@@ -1941,25 +1941,25 @@
         <v>5.555555555555555</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>227.39</v>
+        <v>250.43</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>33.29202424079855</v>
+        <v>33.41186342074332</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>56.48904005627598</v>
+        <v>55.24934496909514</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>44.89053214853726</v>
+        <v>44.33060419491923</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>-0.8535906405699523</v>
+        <v>-0.8665820252336249</v>
       </c>
       <c r="L22" s="11" t="n">
-        <v>-0.7515764103246582</v>
+        <v>-0.779382082940961</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>-0.8025835254473053</v>
+        <v>-0.822982054087293</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>5.555555555555555</v>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q22" s="10" t="n">
-        <v>48.16985200032507</v>
+        <v>53.14645484730876</v>
       </c>
       <c r="R22" s="10" t="n">
-        <v>11.25550989704547</v>
+        <v>10.98773737470539</v>
       </c>
     </row>
   </sheetData>
@@ -2011,7 +2011,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ln(EV/Revenue) = 0.91 + 7.40 x Revenue Growth   ·   R² = 0.53   ·   n = 18   ·   +10 pts of Revenue Growth -&gt; multiple +110%</t>
+          <t>ln(EV/Revenue) = 0.94 + 7.19 x Revenue Growth   ·   R² = 0.49   ·   n = 18   ·   +10 pts of Revenue Growth -&gt; multiple +105%</t>
         </is>
       </c>
     </row>
@@ -2057,16 +2057,16 @@
         <v>0.0425252126851534</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>4.053362204581053</v>
+        <v>4.13214383345701</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>3.234043076989192</v>
+        <v>3.320313226982331</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>3.398643495908821</v>
+        <v>3.483880418261881</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.2533420576310399</v>
+        <v>0.2445042232393575</v>
       </c>
     </row>
     <row r="6">
@@ -2079,16 +2079,16 @@
         <v>0.08126026885982759</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>4.172772737446687</v>
+        <v>4.612093448924637</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>4.584241042180023</v>
+        <v>4.602170227026895</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>4.527505764579889</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>-0.08975712684987069</v>
+        <v>4.603483042618406</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0.002156204879051549</v>
       </c>
     </row>
     <row r="7">
@@ -2101,16 +2101,16 @@
         <v>0.0894753610875106</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>5.347673613101331</v>
+        <v>5.623591628405713</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>4.743835216254207</v>
+        <v>4.79236873892657</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>4.811437143157027</v>
+        <v>4.883752825722325</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.1272890750458913</v>
+        <v>0.1734471896386933</v>
       </c>
     </row>
     <row r="8">
@@ -2123,16 +2123,16 @@
         <v>0.0951246618345723</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>4.923769620571291</v>
+        <v>4.693575265158591</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>5.028488220445414</v>
+        <v>5.136630834597295</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>5.016955671997638</v>
+        <v>5.086327001060017</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>-0.02082506615971491</v>
+        <v>-0.08625411942289962</v>
       </c>
     </row>
     <row r="9">
@@ -2145,16 +2145,16 @@
         <v>0.0956654015764971</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>3.998773008877109</v>
+        <v>4.081135540241491</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>5.180269640728783</v>
+        <v>5.246989087938717</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>5.03708203547393</v>
+        <v>5.106152224883015</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>-0.2280762805399944</v>
+        <v>-0.2221947726891942</v>
       </c>
     </row>
     <row r="10">
@@ -2167,16 +2167,16 @@
         <v>0.1209440480418428</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>11.13936460934935</v>
+        <v>12.40705484282382</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>5.774657417682138</v>
+        <v>5.774834679924379</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>6.0738358663087</v>
+        <v>6.124547871600132</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.9290087365599125</v>
+        <v>1.148469268904904</v>
       </c>
     </row>
     <row r="11">
@@ -2189,16 +2189,16 @@
         <v>0.1230298465241769</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>5.129153217228216</v>
+        <v>5.184206022372479</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>6.261213856852391</v>
+        <v>6.309297181976995</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>6.168363822425484</v>
+        <v>6.217143267784399</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>-0.1808052983823937</v>
+        <v>-0.178322739784461</v>
       </c>
     </row>
     <row r="12">
@@ -2211,16 +2211,16 @@
         <v>0.1333100384365797</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>4.601477513839215</v>
+        <v>4.780065394245846</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>6.83389000654657</v>
+        <v>6.857236780948141</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>6.656196862525871</v>
+        <v>6.694377115053168</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>-0.3266678993324155</v>
+        <v>-0.3029166781105505</v>
       </c>
     </row>
     <row r="13">
@@ -2233,16 +2233,16 @@
         <v>0.136648515175741</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>7.114575450838921</v>
+        <v>5.922275313090807</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>6.803132608771344</v>
+        <v>6.926647350545215</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>6.822775815785168</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>0.04577932843261512</v>
+        <v>6.857106068588005</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>-0.14500117973746</v>
       </c>
     </row>
     <row r="14">
@@ -2255,16 +2255,16 @@
         <v>0.1632637311788301</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>13.83480677407914</v>
+        <v>13.96811173430613</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>8.063216873573712</v>
+        <v>8.053838715896836</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>8.308887850057861</v>
+        <v>8.304186679796606</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.7157924673241978</v>
+        <v>0.7343421226868594</v>
       </c>
     </row>
     <row r="15">
@@ -2277,16 +2277,16 @@
         <v>0.1917087560508048</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>3.133654760726173</v>
+        <v>3.196240666874038</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>11.11226324121541</v>
+        <v>11.02027321156658</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>10.25671958677319</v>
+        <v>10.18991053582952</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>-0.7180003125642811</v>
+        <v>-0.7099672026715861</v>
       </c>
     </row>
     <row r="16">
@@ -2299,16 +2299,16 @@
         <v>0.2088492352512745</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>10.69320613827384</v>
+        <v>7.856065682181051</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>11.72705933607786</v>
+        <v>11.89904736141527</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>11.64458617997387</v>
+        <v>11.52720090218614</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>-0.0881596287846359</v>
+        <v>-0.3397735597174183</v>
       </c>
     </row>
     <row r="17">
@@ -2321,16 +2321,16 @@
         <v>0.2221541930904092</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>48.16985200032507</v>
+        <v>53.14645484730876</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>11.25550989704547</v>
+        <v>10.98773737470539</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>12.85009787572902</v>
+        <v>12.68509430773231</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>3.279668574852346</v>
+        <v>3.836887981110282</v>
       </c>
     </row>
     <row r="18">
@@ -2343,16 +2343,16 @@
         <v>0.2254084426782584</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>10.22646096341891</v>
+        <v>10.73755837380588</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>13.51827451568381</v>
+        <v>13.24823963326811</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>13.1634747483847</v>
+        <v>12.98557651638513</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>-0.2435084114060383</v>
+        <v>-0.1895105560407869</v>
       </c>
     </row>
     <row r="19">
@@ -2365,16 +2365,16 @@
         <v>0.2312227390552258</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>8.883454913853628</v>
+        <v>8.191960082839509</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>14.45123702322237</v>
+        <v>14.34762084931938</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>13.7425251010612</v>
+        <v>13.54027073109704</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>-0.3852806580102183</v>
+        <v>-0.4290370390413463</v>
       </c>
     </row>
     <row r="20">
@@ -2387,16 +2387,16 @@
         <v>0.2429731886212083</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>11.6982158822047</v>
+        <v>13.37774189559688</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>15.51661838958482</v>
+        <v>14.93349784577565</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>14.99168196659414</v>
+        <v>14.73466615456102</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>-0.2460847081180485</v>
+        <v>-0.1041789382665531</v>
       </c>
     </row>
     <row r="21">
@@ -2409,16 +2409,16 @@
         <v>0.2767536858183308</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>24.87181460790544</v>
+        <v>23.63129893865413</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>18.11631771760847</v>
+        <v>17.79270811442963</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>19.25184121254</v>
+        <v>18.78813397878188</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.3728956952289946</v>
+        <v>0.3281451472521764</v>
       </c>
     </row>
     <row r="22">
@@ -2431,16 +2431,16 @@
         <v>0.2916598872820696</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>23.17396364875435</v>
+        <v>23.11562095109607</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>21.0199366412188</v>
+        <v>20.29695721196258</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>21.49826838279597</v>
+        <v>20.91492884229838</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.1024754281757272</v>
+        <v>0.1388712460541737</v>
       </c>
     </row>
     <row r="24">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="B28" s="17" t="n">
-        <v>0.5298918011065868</v>
+        <v>0.489015800459894</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="B29" s="17" t="n">
-        <v>0.2927752511328587</v>
+        <v>0.2625959399792598</v>
       </c>
       <c r="C29" t="inlineStr"/>
     </row>
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="B30" s="17" t="n">
-        <v>0.01240295018953297</v>
+        <v>0.01316182774043673</v>
       </c>
       <c r="C30" t="inlineStr"/>
     </row>
